--- a/artfynd/A 27913-2024 artfynd.xlsx
+++ b/artfynd/A 27913-2024 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17263249</v>
+        <v>17263252</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1365</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577584.3784069472</v>
+        <v>577584</v>
       </c>
       <c r="R2" t="n">
-        <v>6971340.875030146</v>
+        <v>6971341</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -752,19 +747,9 @@
           <t>2014-07-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-07-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,42 +785,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17263067</v>
+        <v>17263077</v>
       </c>
       <c r="B3" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -844,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577584.3784069472</v>
+        <v>577584</v>
       </c>
       <c r="R3" t="n">
-        <v>6971340.875030146</v>
+        <v>6971341</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -877,19 +857,9 @@
           <t>2014-07-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-07-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,42 +895,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>17263068</v>
+        <v>17263074</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -969,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577584.3784069472</v>
+        <v>577584</v>
       </c>
       <c r="R4" t="n">
-        <v>6971340.875030146</v>
+        <v>6971341</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1002,19 +967,9 @@
           <t>2014-07-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2014-07-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,42 +1005,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>17263074</v>
+        <v>17263068</v>
       </c>
       <c r="B5" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1094,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577584.3784069472</v>
+        <v>577584</v>
       </c>
       <c r="R5" t="n">
-        <v>6971340.875030146</v>
+        <v>6971341</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1127,19 +1077,9 @@
           <t>2014-07-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2014-07-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,15 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>17263245</v>
+        <v>17263067</v>
       </c>
       <c r="B6" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,21 +1126,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219880</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1219,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577584.3784069472</v>
+        <v>577584</v>
       </c>
       <c r="R6" t="n">
-        <v>6971340.875030146</v>
+        <v>6971341</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -1252,19 +1187,9 @@
           <t>2014-07-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2014-07-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,15 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>17263252</v>
+        <v>17263245</v>
       </c>
       <c r="B7" t="n">
-        <v>98493</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,21 +1236,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1365</v>
+        <v>219880</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1344,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577584.3784069472</v>
+        <v>577584</v>
       </c>
       <c r="R7" t="n">
-        <v>6971340.875030146</v>
+        <v>6971341</v>
       </c>
       <c r="S7" t="n">
         <v>100</v>
@@ -1377,19 +1297,9 @@
           <t>2014-07-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2014-07-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,42 +1335,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>17263077</v>
+        <v>17263249</v>
       </c>
       <c r="B8" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1469,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577584.3784069472</v>
+        <v>577584</v>
       </c>
       <c r="R8" t="n">
-        <v>6971340.875030146</v>
+        <v>6971341</v>
       </c>
       <c r="S8" t="n">
         <v>100</v>
@@ -1502,19 +1407,9 @@
           <t>2014-07-15</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2014-07-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 27913-2024 artfynd.xlsx
+++ b/artfynd/A 27913-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17263252</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17263077</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17263074</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17263068</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17263067</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17263245</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,8 +1477,22 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17263249</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>